--- a/downloads/agent-authority-review.xlsx
+++ b/downloads/agent-authority-review.xlsx
@@ -252,7 +252,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -321,8 +321,26 @@
       <color rgb="00183D32"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Source Serif 4"/>
+      <b val="1"/>
+      <color rgb="00F5F0E6"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Figtree"/>
+      <color rgb="00F5F0E6"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Figtree"/>
+      <b val="1"/>
+      <color rgb="00F5F0E6"/>
+      <sz val="11"/>
+      <u val="single"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -351,6 +369,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E5EBE1"/>
         <bgColor rgb="00E5EBE1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00183D32"/>
+        <bgColor rgb="00183D32"/>
       </patternFill>
     </fill>
   </fills>
@@ -390,7 +414,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -437,6 +461,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2431,7 +2464,11 @@
       <c r="F40" s="1" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n"/>
+      <c r="A41" s="18" t="inlineStr">
+        <is>
+          <t>The Living Craft cohort</t>
+        </is>
+      </c>
       <c r="B41" s="1" t="n"/>
       <c r="C41" s="1" t="n"/>
       <c r="D41" s="1" t="n"/>
@@ -2439,7 +2476,11 @@
       <c r="F41" s="1" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n"/>
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>Decide where the agent may act and where people retain authority. Explore The Living Craft’s October 2026 cohort: 30 live hours with Sunil Mathew, plus independent work.</t>
+        </is>
+      </c>
       <c r="B42" s="1" t="n"/>
       <c r="C42" s="1" t="n"/>
       <c r="D42" s="1" t="n"/>
@@ -2447,7 +2488,11 @@
       <c r="F42" s="1" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n"/>
+      <c r="A43" s="20" t="inlineStr">
+        <is>
+          <t>Apply at https://learning.thelivingcraft.ai/#apply</t>
+        </is>
+      </c>
       <c r="B43" s="1" t="n"/>
       <c r="C43" s="1" t="n"/>
       <c r="D43" s="1" t="n"/>
@@ -3712,10 +3757,13 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId1"/>
+  </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
 </worksheet>
 </file>
 
